--- a/samples/教員裁量点_○○先生.xlsx
+++ b/samples/教員裁量点_○○先生.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daiji\Downloads\2026\eclass\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\daiji\temp\ducis-lab-assignment\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032BB6CD-2F26-491E-B291-4576E271790D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0EDF07-C4AB-4851-91A1-3E33DBCA96D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42450" yWindow="2010" windowWidth="18450" windowHeight="14475" xr2:uid="{FDF0FD57-EB3B-4630-882A-2BF445BFB9BB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="32640" windowHeight="21120" xr2:uid="{FDF0FD57-EB3B-4630-882A-2BF445BFB9BB}"/>
   </bookViews>
   <sheets>
     <sheet name="教員裁量点" sheetId="1" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
   <si>
     <t>学生ID</t>
   </si>
@@ -187,6 +187,9 @@
   <si>
     <t>◇◇　◇◇</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>○○　○○</t>
   </si>
 </sst>
 </file>
@@ -636,7 +639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/excel/2006/main" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{80A4FE86-8D6C-4374-9A7D-F4B3EFB2B37D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80A4FE86-8D6C-4374-9A7D-F4B3EFB2B37D}">
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -667,11 +670,11 @@
       <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2">
-        <v>59</v>
+      <c r="C2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="2">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -681,11 +684,11 @@
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3">
-        <v>14</v>
+      <c r="C3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="2">
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -695,11 +698,11 @@
       <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4">
-        <v>58</v>
+      <c r="C4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="2">
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -709,11 +712,11 @@
       <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
+      <c r="C5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="2">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -723,11 +726,11 @@
       <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6">
-        <v>26</v>
+      <c r="C6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -737,11 +740,11 @@
       <c r="B7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
+      <c r="C7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="2">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -751,11 +754,11 @@
       <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8">
-        <v>51</v>
+      <c r="C8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -765,11 +768,11 @@
       <c r="B9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9">
-        <v>46</v>
+      <c r="C9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="2">
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -779,11 +782,11 @@
       <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10">
-        <v>39</v>
+      <c r="C10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -793,27 +796,27 @@
       <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="2">
         <v>25</v>
-      </c>
-      <c r="D11">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing ns3:id="rId1"/>
+  <legacyDrawing r:id="rId1"/>
   <extLst>
-    <ext uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <ns4:dataValidations count="1">
-        <ns4:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" ns2:uid="{454F2B0F-4ABB-429A-ACCA-3D5BA3425E7F}">
-          <ns4:formula1>
-            <ns5:f>教員氏名リスト!$A$2:$A$5</ns5:f>
-          </ns4:formula1>
-          <ns5:sqref>C2:C11</ns5:sqref>
-        </ns4:dataValidation>
-      </ns4:dataValidations>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C122CEC0-4B1F-4800-8F8E-96FC6C425694}">
+          <x14:formula1>
+            <xm:f>教員氏名リスト!$A$2:$A$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C11</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
     </ext>
   </extLst>
 </worksheet>
